--- a/گزارش/لیست شرکتها/Kazakhstan_Companies.xlsx
+++ b/گزارش/لیست شرکتها/Kazakhstan_Companies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>توضیحات و زمینه دقیق مصرف</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>وضعیت صحت‌سنجی (سپتامبر ۲۰۲۶)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -527,6 +532,11 @@
           <t>بزرگترین کارخانه صنایع شیرینی و شکلات قزاقستان با دو مجتمع عظیم در آلماتی و چیمکنت؛ خریدار واگنی و کانتینری جوش شیرین خوراکی.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت، ایمیل، آدرس و تلفن با منابع رسمی مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -582,6 +592,11 @@
           <t>مجتمع بزرگ شیرینی و بیسکویت در شمال قزاقستان با صادرات گسترده به CIS؛ خرید مستقیم و متناوب از طریق دپارتمان تدارکات مواد اولیه (OMTS).</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — همه اطلاعات با منابع مستقل مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -614,7 +629,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://hamle-kompani-ltd.pulscen.kz</t>
+          <t>http://www.hamle.kz</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -635,6 +650,11 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>زیرمجموعه هلدینگ غذایی پلادیس با کارخانه بزرگ در کاسکلن آلماتی؛ مصرف ماهانه ده‌ها تن جوش شیرین خوراکی.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>🔴 اصلاح شد — وبسایت فایل اصلی یک صفحه آگهی در pulscen.kz بود نه سایت رسمی؛ سایت درست hamle.kz است. شماره پلاک (۳A) به آدرس اضافه شد.</t>
         </is>
       </c>
     </row>
@@ -692,6 +712,11 @@
           <t>بزرگترین مجتمع نان و شیرینی قزاقستان با تولید روزانه بیش از ۱۵۰ تن فرآورده؛ نیازمند تأمین مداوم نمک‌های قلیایی و بهبوددهنده‌ها.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت و آدرس درست است. ایمیل دوم (aksaynan@aksaynan.kz) و تلفن مستقیماً تأیید نشد؛ منابع رسمی از reception@aksaynan.kz و +7(727)330-31-xx نام می‌برند.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -747,6 +772,11 @@
           <t>تولیدکننده پیشرو سس مایونز، کچاپ، مارگارین و روغن در آلماتی و قره‌غال؛ مصرف‌کننده نمک‌های بافری و خنثی‌کننده اسیدیته.</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — کاملاً مطابق با منابع رسمی.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -802,6 +832,11 @@
           <t>بزرگترین تولیدکننده کنسرو و فرآورده‌های گوشتی در غرب قزاقستان؛ دارای کارخانه خوراک و مکمل‌سازی پروتئینی دامپروری.</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت، آدرس و تلفن مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -857,6 +892,11 @@
           <t>بزرگترین تولیدکننده خوراک دام و طیور جنوب قزاقستان؛ خریدار تناژ بالای جوش شیرین دامی جهت پیشگیری از اسیدوز در گله‌های شیری.</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت و تلفن مطابق است.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -912,6 +952,11 @@
           <t>معتبرترین شرکت داروسازی قزاقستان در شیمکنت؛ خریدار منظم بی‌کربنات سدیم گرید دارویی با اندوتوکسین پایین جهت سرم‌ها و آنتی‌اسیدها.</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد (با یک نکته جزئی) — کد پستی آدرس در یک منبع 160019 ذکر شده نه 160018؛ تفاوت جزئی، نیاز به تأیید نهایی ندارد.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -967,6 +1012,11 @@
           <t>تخصصی‌ترین خط تولید سرم‌های درمانی قزاقستان؛ مصرف مداوم ماده مؤثره جوش شیرین دارویی در فرمولاسیون سرم‌های اسیدوز متابولیک.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — با یک اختلاف املایی جزئی: نام روستا در ثبت رسمی «Кокузек» ضبط شده نه «Кокозек».</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1022,6 +1072,11 @@
           <t>از تولیدکنندگان برتر دارویی وابسته به هلدینگ Nobel Ilac با خطوط فعال ساخت قرص‌های جوشان و داروهای گوارشی.</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — کاملاً مطابق با منابع رسمی.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1077,6 +1132,11 @@
           <t>واحد داروسازی مدرن با سرمایه‌گذاری مشترک Abdi Ibrahim ترکیه و قزاقستان؛ مصرف‌کننده نمک‌های دارویی با استانداردهای فارماکوپه‌ای.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت، ایمیل و آدرس دفتر فروش مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1132,6 +1192,11 @@
           <t>تأمین‌کننده کلان مواد شیمیایی پروژه‌های نفتی قره‌چغانک و کاشاگان با انبارهای وسیع در اورالسک و آتیرائو.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — کاملاً مطابق با منابع رسمی.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1187,6 +1252,11 @@
           <t>تأمین مستقیم مواد شیمیایی معدنی سنگین از جمله بی‌کربنات سدیم صنعتی در بسته‌بندی جامبوبگ برای عملیات حفاری میدان‌های نفتی.</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — کاملاً مطابق با منابع رسمی.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1242,6 +1312,11 @@
           <t>ارائه‌دهنده مواد شیمیایی مهندسی به پالایشگاه‌ها و صنایع هیدروکربوری در غرب و مرکز قزاقستان.</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>🟡 نیاز به بررسی بیشتر — آدرس «Коргалжынское шоссе, 3Б» تأیید نشد؛ منابع اخیر (2GIS) آدرس فعلی را «ул. Динмухамед Конаев, 14/3» ذکر می‌کنند. ممکن است دفتر جابجا شده باشد.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1297,6 +1372,11 @@
           <t>بزرگترین شبکه انبارهای شیمیایی قزاقستان با ۵ انبار لجستیکی در آلماتی، آستانه، شیمکنت، قره‌غال و پاولودار؛ واردکننده رسمی تناژ بالا.</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت، ایمیل، آدرس و تلفن دقیقاً مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1314,7 +1394,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>شبکه فدرال تأمین مواد اولیه صنعتی، متالورژی و شیمیایی</t>
+          <t>شبکه فدرال تأمین مواد اولیه صنعتی، متالورژی و شیمیایی (فروشنده مستقیم سدیم بی‌کربنات نیز هست)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1349,7 +1429,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>تأمین‌کننده سراسری در شهرهای آستانه، آلماتی و آکتوبه؛ توزیع انواع گریدهای بی‌کربنات سدیم جهت مصارف متالورژی، تصفیه و ایمنی.</t>
+          <t>تأمین‌کننده سراسری در شهرهای آستانه، آلماتی، اوسط‌کامنوگرسک، قره‌غاندی، پتروپاولوفسک و آکتوبه؛ این شرکت مستقیماً «сода пищевая / بی‌کربنات سدیم» را به‌صورت کیسه ۲۵ کیلویی و تن فله برای صنایع غذایی در کاتالوگ آنلاین خود (بخش soda-pishchevaya در هر شعبه) می‌فروشد — گزینه بسیار معتبر برای تماس.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد (اصلاح از بررسی قبلی) — با جست‌وجوی دقیق‌تر مشخص شد که این شرکت واقعاً و مستقیماً «сода пищевая» (بی‌کربنات سدیم خوراکی) را در کاتالوگ رسمی خودش می‌فروشد — در شعبه‌های آلماتی، اوسط‌کامنوگرسک، قره‌غاندی، پتروپاولوفسک، آکتوبه و قوستانای صفحه اختصاصی «soda-pishchevaya» دارد. نگرانی قبلی من (که فقط فلز می‌فروشند) اشتباه بود؛ این یکی از بهترین گزینه‌های این لیست است. ایمیل و تلفن شعبه آلماتی (alm@snabtechmet.kz / +7727 312-38-39) هم دقیقاً با فایل مطابقت دارد.</t>
         </is>
       </c>
     </row>
@@ -1407,6 +1492,11 @@
           <t>شرکت تخصصی تأمین مواد شیمیایی پایه و اسیدها در منطقه صنعتی قره‌غال با شبکه فروش به صنایع غذایی و معدنی.</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — کاملاً مطابق با منابع رسمی.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1462,6 +1552,11 @@
           <t>تأمین‌کننده معتبر با بیش از ۲۵ سال سابقه در توزیع مواد شیمیایی خلوص بالا، نمک‌های سدیم و اسیدها در آلماتی.</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — این شرکت حتی مستقیماً «سدا پیشه‌وی/جوش شیرین (NaHCO3)» را در کاتالوگ محصولات خود دارد؛ گزینه بسیار مناسبی برای تماس است.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1517,6 +1612,11 @@
           <t>شعبه هلدینگ اروپایی Eligita در آسیای میانه؛ تأمین‌کننده مواد اولیه و بیکینگ‌پودرهای صنعتی برای کارخانجات نان و قنادی.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — کاملاً مطابق با منابع رسمی.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1572,6 +1672,11 @@
           <t>کارخانه پیشرو تولید پودرها و مایعات پاک‌کننده در آلماتی؛ مصرف‌کننده بی‌کربنات سدیم صنعتی به عنوان قلیایی‌ساز و ساینده غیرمخرب.</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت، آدرس و تلفن مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1627,6 +1732,11 @@
           <t>تولیدکننده فرآورده‌های گوشتی حلال، سوسیس و خمیرهای منجمد پرشده با خطوط صنعتی خودکار؛ مصرف‌کننده نمک‌های بافری و بی‌کربنات خوراکی.</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد (با نکته جزئی) — پلاک دقیق در منابع مختلف بین 142/55 و 145/55 متفاوت ذکر شده؛ یک آدرس دیگر (ул. Дулатова 52б) هم برای دفتر فروش دیده شد.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1634,12 +1744,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ТОО «Шин-Лайн» (Бренд «Chickodelli»)</t>
+          <t>ТОО «Прима Кус» (Бренд «Chickodelli»)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CHICKODELLI (Shin-Line Group)</t>
+          <t>CHICKODELLI (Prima Kus LLP)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1654,22 +1764,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Алматинская обл., Илийский р-н, с. Байсерке, ул. Султана Бейбарса, 1</t>
+          <t>г. Алматы, ул. Тимирязева, 28В, офис 304 (کارخانه: Алматинская обл., Уйгурский р-н, Кыргызсайский с/о, с. Рахат)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://shin-line.com</t>
+          <t>https://chickodelli.kz</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>info@shin-line.com</t>
+          <t>نامشخص - نیاز به تماس مستقیم (ایمیل قبلی info@shin-line.com متعلق به شرکت دیگری بود)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>+7 (727) 390-80-00</t>
+          <t>+7 (771) 771-77-47</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1680,6 +1790,11 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>بخش فرآورده‌های پروتئینی و سوخاری گروه بزرگ شین‌لاین؛ تولیدکننده ناگت و برگر سوخاری با مصرف بی‌کربنات سدیم در پوشش‌های خمیری.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🔴 اصلاح بزرگ — برند «Chickodelli» متعلق به شرکت «Шин-Лайн» (تولیدکننده بستنی) نیست؛ متعلق به شرکت کاملاً متفاوتی به نام ТОО «Прима Кус» است. وبسایت shin-line.com واقعی است اما مربوط به یک شرکت بستنی‌سازی بی‌ربط. نام شرکت، آدرس، وبسایت و تلفن اصلاح شد؛ ایمیل رسمی جدید یافت نشد.</t>
         </is>
       </c>
     </row>
@@ -1737,6 +1852,11 @@
           <t>تأمین‌کننده و توزیع‌کننده عمده مواد شیمیایی و غذایی برای کارخانجات صنایع نان، قنادی و فرآورده‌های گوشتی قزاقستان.</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>🟡 نیاز به بررسی بیشتر — آدرس فایل (Бостандыкский район, ул. Ергожина, 17А) در یک منبع دیده شد، اما جدیدترین منبع آدرس دیگری (ул. Шевченко/Радостовца 165Б) نشان می‌دهد. ممکن است دفتر جابجا شده باشد.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1792,6 +1912,11 @@
           <t>شعبه هلدینگ بین‌المللی Neos Ingredients در قزاقستان؛ واردکننده مستقیم استابیلایزرها، بیکینگ‌پودرها و جوش شیرین خوراکی.</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — آدرس با ثبت رسمی مطابقت دارد (Тимирязева 42/21). وبسایت مربوط به شرکت مادر روسی است که با توضیح فایل («شعبه هلدینگ») سازگار است.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1847,6 +1972,11 @@
           <t>تولیدکننده شناخته‌شده ماکارونی و سبد گسترده محصولات منجمد خمیری-گوشتی (پلمنی، مانتی، خینکالی، وارنیکی) با مصرف نمک‌های بافری و بی‌کربنات خوراکی.</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت و فعالیت مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1902,6 +2032,11 @@
           <t>از بزرگترین کارخانجات فرآوری گوشت جنوب قزاقستان با تولید روزانه ۱۵ الی ۲۰ تن سوسیس و کالباس؛ مصرف‌کننده تثبیت‌کننده‌های پروتئین.</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — آدرس کارخانه و دفتر فروش هر دو مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1934,7 +2069,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://karagandy-nan.kz</t>
+          <t>https://www.selprom.kz</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1955,6 +2090,11 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>بزرگترین مجتمع نان و شیرینی قزاقستان مرکزی با بیش از ۹۰ سال قدمت؛ مصرف‌کننده دائمی جوش شیرین خوراکی در خطوط بیسکویت و پریانیک صنعتی.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>🔴 اصلاح شد — دامنه karagandy-nan.kz در هیچ منبعی یافت نشد و ظاهراً فعال نیست؛ سایت رسمی فعلی selprom.kz است. ایمیل مطابقت داشت.</t>
         </is>
       </c>
     </row>
@@ -2012,6 +2152,11 @@
           <t>کارخانه بین‌المللی با تولید بیش از ۴۰ هزار تن نودل فوری؛ مصرف‌کننده مداوم بی‌کربنات سدیم در محلول قلیایی عمل‌آوری خمیر نودل.</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت و آدرس کارخانه مطابقت دارد (نام شهر «Konaev/Kapshagai» احتمالاً با نام جدید «شهر آلاتائو» جایگزین شده است).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2067,6 +2212,11 @@
           <t>غول صنعتی تولید آرد، ماکارونی، نان و بیسکویت در شمال قزاقستان؛ مصرف‌کننده افزودنی‌های حجم‌دهنده و بی‌کربنات خوراکی در سالن‌های پخت بیسکویت.</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت و آدرس مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2094,7 +2244,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Алматинская обл., Карасайский р-н, г. Каскелен, ул. Абая, 1</t>
+          <t>Алматинская обл., Карасайский р-н, г. Каскелен, ул. Достык, 4Д</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2120,6 +2270,11 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>کارخانه معتبر تولید شکلات، آبنبات، بیسکویت و ویفر در حومه آلماتی (کاسکلن)؛ مصرف‌کننده مستمر جوش شیرین در پخت ورقه‌های ویفر و کلوچه‌ها.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🔴 اصلاح شد — آدرس «ул. Абая, 1» در هیچ منبعی تأیید نشد؛ کاتالوگ رسمی شرکت آدرس «ул. Достык, 4Д» در کاسکلن را ذکر می‌کند. وبسایت و ایمیل درست بود.</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2304,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>г. Алматы, Турксибский район, пр. Сейфуллина / ул. Жетысуская</t>
+          <t>с. Косшы (Ақмола/نزدیک آستانه), ул. Абай, 36 (آدرس قبلی «آلماتی» اشتباه بود)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2175,6 +2330,11 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>تولیدکننده عمده غذاهای نیمه‌آماده خمیری منجمد با مصرف بی‌کربنات سدیم جهت حفظ کشسانی گلوتن خمیر در شوک انجماد.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🔴 اصلاح بزرگ — این کارخانه در روستای «قوشی» نزدیک آستانه واقع است، نه در آلماتی همان‌طور که در فایل آمده بود. وبسایت درست بود.</t>
         </is>
       </c>
     </row>
@@ -2184,52 +2344,57 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ТОО «Prime Food Factory» (Бренд «Самса Шеф»)</t>
+          <t>ТОО «SMAK-PV» (برند «Павлодарский Смак»)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PRIME FOOD FACTORY, LLP</t>
+          <t>SMAK-PV LLP (Pavlodarsky Smak)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>تولیدکننده صنعتی سمبوسه سنتی، خمیر لایه‌ای و پیراشکی منجمد</t>
+          <t>بزرگترین تولیدکننده نیمه‌آماده‌های منجمد خمیری در قزاقستان (پلمنی، منتی، خمیر، سمبوسه)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>خوراکی (E500ii) - ورآورنده و کنترل‌کننده بافت خمیرهای چندلایه پفکی</t>
+          <t>خوراکی (E500ii) - ورآورنده و کنترل‌کننده بافت خمیرهای منجمد و لایه‌ای</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>г. Алматы, Алатауский район, микрорайон Алгабас</t>
+          <t>г. Павлодар, ул. Естая, 136/1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://samsachef.kz</t>
+          <t>https://cmak-pv.kz</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>info@samsachef.kz</t>
+          <t>smak-pavlodar@mail.ru</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+7 (701) 055-55-40 / +7 (727) 344-00-11</t>
+          <t>+7 (7182) 50-87-73</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>FoodExpo Qazaqstan 2025</t>
+          <t>جایگزینی تأیید شده به‌جای ردیف اصلی که قابل تأیید نبود</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>بزرگترین کارخانه تخصصی تولید سمبوسه و نیمه‌آماده‌های لایه‌ای در قزاقستان؛ مصرف‌کننده بی‌کربنات سدیم برای دستیابی به بافت ترد ورقه‌های خمیر.</t>
+          <t>بزرگترین تولیدکننده نیمه‌آماده‌های منجمد قزاقستان با ۲۵+ سال سابقه (از ۱۹۹۹)، تولید ماهانه ۳۵۰-۴۰۰ تن؛ خودشان را «تولیدکننده شماره ۱ پلمنی در قزاقستان» معرفی می‌کنند. برندها: Смак، Кроха، Забава، Султан. مصرف‌کننده بی‌کربنات سدیم برای بافت خمیرهای منجمد (پلمنی، مانتی، خمیر لایه‌ای).</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🔵 جایگزین شد — شرکت اصلی «Prime Food Factory / Самса Шеф» قابل تأیید نبود (وبسایت samsachef.kz در هیچ منبعی دیده نشد و شرکت ثبت‌شده با نام مشابه در شیمکنت است نه آلماتی). به‌جای آن، ТОО «SMAK-PV» (Павлодарский Смак) را جایگزین کردم — یک تولیدکننده کاملاً معتبر و بزرگ نیمه‌آماده‌های منجمد خمیری با بیش از ۲۵ سال سابقه که آدرس، وبسایت، ایمیل و تلفنش همگی از منابع مستقل تأیید شد.</t>
         </is>
       </c>
     </row>
@@ -2239,52 +2404,57 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ТОО «Свит Премиум»</t>
+          <t>ТОО «Кондитерская фабрика Сауле»</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SWEET PREMIUM, LLP</t>
+          <t>Saule Confectionery Factory LLP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>کارخانه تولید شیرینی، کوکی و ویفر</t>
+          <t>کارخانه بزرگ تولید بیسکویت، ویفر و شیرینی خشک (صادرکننده منطقه‌ای)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>خوراکی (E500ii) - حجم‌دهنده و خمیرمایه شیمیایی بیسکویت و کوکی</t>
+          <t>خوراکی (E500ii) - حجم‌دهنده و خمیرمایه شیمیایی بیسکویت و ویفر</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Алматинская обл., Карасайский район, с.о. Райымбек</t>
+          <t>Жамбылская обл., г. Тараз, район Әулиеата, просп. Жамбыла, стр. 3Б</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://sweetpremium.kz</t>
+          <t>https://www.saulecompany.com</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>info@sweetpremium.kz</t>
+          <t>برای تماس مستقیم، فرم تماس سایت saulecompany.com (ایمیل رسمی عمومی یافت نشد)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+7 (727) 317-22-33</t>
+          <t>از طریق سایت رسمی یا صفحه استخدام hh.kz قابل دریافت است</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>FoodExpo Qazaqstan 2024</t>
+          <t>جایگزینی تأیید شده به‌جای ردیف اصلی که با فایل مطابقت نداشت</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>تولیدکننده فرآورده‌های شیرینی و ویفر در آلماتی با خریدهای مستمر نمک‌های قلیایی E500ii در کیسه‌های ۲۵ کیلوگرمی.</t>
+          <t>یکی از تولیدکنندگان پیشرو بیسکویت و ویفر در قزاقستان (بیش از ۸۰ قلم محصول) با تجهیزات اتریشی/سوئیسی/دانمارکی؛ صادرات به قرقیزستان، روسیه، چین، تاجیکستان، مغولستان، گرجستان و ازبکستان. درآمد سالانه تخمینی ~۴ میلیارد تنگه (۲۰۲۰). مصرف‌کننده مستمر جوش شیرین در خطوط بیسکویت و ویفر.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>🔵 جایگزین شد — شرکت اصلی «Sweet Premium» بررسی شد و مشخص شد یک واردکننده/توزیع‌کننده دسرهای منجمد اروپایی برای بخش HoReCa است (طبق ثبت رسمی: «خرده‌فروشی نان و شیرینی»)، نه یک کارخانه تولیدکننده بیسکویت/ویفر با مصرف مستقیم جوش شیرین. به‌جای آن، ТОО «Кондитерская фабрика Сауле» در تراز را جایگزین کردم — یک کارخانه واقعی و بزرگ تولید بیسکویت/ویفر با سابقه صادراتی که آدرس و وبسایتش از منابع رسمی (ثبت شرکت + سایت رسمی) تأیید شد.</t>
         </is>
       </c>
     </row>
@@ -2342,6 +2512,11 @@
           <t>شرکت رسمی ثبت‌شده قزاقستان و غرفه‌دار نمایشگاه اینترفود آستانه؛ ارائه‌دهنده اسنک‌های ذرت با طعم‌های میوه‌ای و پاپ‌کورن تحت برند EPIC FOOD با مصرف جوش شیرین در انبساط اکستروژنی.</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>✅ تأیید نسبی — شرکت «ТОО NOMAD GROUP RBS» با БИН 080540018440 که در فایل ذکر شده، در ثبت رسمی شرکت‌های قزاقستان دقیقاً با همین شماره و به‌صورت «فعال» ثبت شده (از سال ۲۰۰۸)؛ این تأیید هویت حقوقی شرکت است. وبسایت و اطلاعات تماس دقیق به‌صورت مستقل تأیید نشد.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2397,6 +2572,11 @@
           <t>هاب منطقه‌ای هلدینگ بین‌المللی United Trading System؛ از بزرگترین واردکنندگان رسمی مواد شیمیایی خام، اسیدها و بی‌کربنات سدیم در قزاقستان.</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت و ساختار هلدینگ مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2429,7 +2609,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://progast.sk</t>
+          <t>https://www.progast.kz</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2450,6 +2630,11 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>نمایندگی رسمی کمپانی اروپایی Progast؛ واردکننده و فرمولاتور افزودنی‌های عمل‌آوری گوشت، فسفات‌ها و بافرهای اسیدیته برای سوسیس و کالباس.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🔴 اصلاح شد — وبسایت «progast.sk» متعلق به دفتر لهستان/اسلواکی این شرکت است، نه قزاقستان؛ سایت درست progast.kz است. دفتر مرکزی این شرکت در واقع در پاولودار است و آلماتی یکی از شعبه‌هاست.</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2664,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>г. Алматы, Медеуский район, ул. Толе би, 13</t>
+          <t>г. Алматы, Медеуский район, ул. Тулебаева, 13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2505,6 +2690,11 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>تولیدکننده فرآورده‌های خمیری، نان پیده، لحم‌عجون و نیمه‌آماده‌های منجمد رستورانی در قزاقستان.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>🔴 اصلاح شد — نام خیابان «Толе би» اشتباه بود؛ آدرس درست «ул. Тулебаева, 13» است (دو خیابان با املای مشابه در آلماتی). وبسایت و ایمیل درست بود.</t>
         </is>
       </c>
     </row>
@@ -2562,6 +2752,11 @@
           <t>هاب توزیع افزودنی‌ها، طعم‌دهنده‌ها و نمک‌های سدیم برای کارخانجات صنایع گوشت، لبنیات و فرآوری قزاقستان.</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — این شرکت شعبه گروه روسی BIOSTAR است، مطابق توضیح فایل.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2617,6 +2812,11 @@
           <t>تولیدکننده صنعتی پلمنی، مانتی، وارنیکی با مصرف بی‌کربنات خوراکی جهت تثبیت ساختار خمیر در سرمایش و پخت بدون وا رفتگی.</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — آدرس دقیقاً با ثبت رسمی مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2672,6 +2872,11 @@
           <t>تولید روزانه بیش از ۹۰,۰۰۰ عدد نان برگر و فرآورده‌های آردی در پایتخت قزاقستان؛ مصرف‌کننده مستقیم نمک‌های بی‌کربنات برای هوادهی و بافت یکنواخت نان.</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — وبسایت، آدرس (ул. Бейсекбаева, 28) و ایمیل دقیقاً با منابع رسمی مطابقت دارد.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2725,6 +2930,11 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>بزرگترین مجتمع گوشت بوقلمون قزاقستان؛ دارای کارخانه خوراک‌سازی اختصاصی با مصرف بی‌کربنات سدیم دامی برای تنظیم موازنه الکترولیت و اسیدیته جیره طیور.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>✅ تأیید شد — آدرس و تلفن دقیقاً مطابقت دارد.</t>
         </is>
       </c>
     </row>
